--- a/artfynd/A 20658-2026 artfynd.xlsx
+++ b/artfynd/A 20658-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124812376</v>
+        <v>119721840</v>
       </c>
       <c r="B2" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,44 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Övre Skogs gamla tomter, Övre Skogs gamla tomter, Dlr</t>
+          <t>Övre Skogs gamla tomter, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521502</v>
+        <v>521558</v>
       </c>
       <c r="R2" t="n">
-        <v>6719888</v>
+        <v>6719793</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,27 +747,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Ullticka på relativ ny granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,21 +776,169 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Övre Skogs gamla tomter där skogen varit obrukad, på kanten till tidigare åkermark. Fuktig miljö med dike och surdrog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Maria Warg</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Maria Warg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>124812376</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Övre Skogs gamla tomter, Övre Skogs gamla tomter, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>521502</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6719888</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Karl Ericson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Karl Ericson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20658-2026 artfynd.xlsx
+++ b/artfynd/A 20658-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -817,6 +822,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119721840</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -939,8 +949,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124812376</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>